--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_77_R8.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_77_R8.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>K. HAYES</t>
+          <t>N. NEDOVIC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.4336</v>
+        <v>3.8574</v>
       </c>
       <c r="E2" t="n">
-        <v>2.9649</v>
+        <v>1.9368</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4687</v>
+        <v>1.9206</v>
       </c>
       <c r="G2" t="n">
-        <v>2.2757</v>
+        <v>2.6342</v>
       </c>
       <c r="H2" t="n">
-        <v>1.9376</v>
+        <v>0.8307</v>
       </c>
       <c r="I2" t="n">
-        <v>0.338</v>
+        <v>1.8034</v>
       </c>
       <c r="J2" t="n">
-        <v>1.9149</v>
+        <v>3.049</v>
       </c>
       <c r="K2" t="n">
-        <v>1.7309</v>
+        <v>0.9278</v>
       </c>
       <c r="L2" t="n">
-        <v>0.184</v>
+        <v>2.1212</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3607</v>
+        <v>-0.4148</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2067</v>
+        <v>-0.097</v>
       </c>
       <c r="O2" t="n">
-        <v>0.154</v>
+        <v>-0.3178</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6959</v>
+        <v>-0.232</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R2" t="n">
-        <v>0.6959</v>
+        <v>0.9278</v>
       </c>
       <c r="S2" t="n">
-        <v>1.8178</v>
+        <v>0.5247000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>1.0499</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7679</v>
+        <v>0.619</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.3558</v>
+        <v>0.9304</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.3558</v>
+        <v>0.7886</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>N. NEDOVIC</t>
+          <t>J. BLOSSOMGAME</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3616</v>
+        <v>3.0432</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5083</v>
+        <v>3.0183</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8534</v>
+        <v>0.0249</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6342</v>
+        <v>0.2766</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8307</v>
+        <v>0.2197</v>
       </c>
       <c r="I3" t="n">
-        <v>1.8034</v>
+        <v>0.0569</v>
       </c>
       <c r="J3" t="n">
-        <v>3.049</v>
+        <v>1.9105</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9278</v>
+        <v>1.4823</v>
       </c>
       <c r="L3" t="n">
-        <v>2.1212</v>
+        <v>0.4282</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.4148</v>
+        <v>-1.6339</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.097</v>
+        <v>-1.2626</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3178</v>
+        <v>-0.3713</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.232</v>
+        <v>1.6237</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9278</v>
+        <v>1.6237</v>
       </c>
       <c r="S3" t="n">
-        <v>0.029</v>
+        <v>0.0707</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5228</v>
+        <v>0.0356</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5518</v>
+        <v>0.0351</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9304</v>
+        <v>1.0722</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1418</v>
+        <v>1.0722</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7886</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. BLOSSOMGAME</t>
+          <t>K. HAYES</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.7326</v>
+        <v>2.7498</v>
       </c>
       <c r="E4" t="n">
-        <v>2.7077</v>
+        <v>2.2139</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0249</v>
+        <v>0.5359</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2766</v>
+        <v>2.2757</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2197</v>
+        <v>1.9376</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0569</v>
+        <v>0.338</v>
       </c>
       <c r="J4" t="n">
-        <v>1.9105</v>
+        <v>1.9149</v>
       </c>
       <c r="K4" t="n">
-        <v>1.4823</v>
+        <v>1.7309</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4282</v>
+        <v>0.184</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.6339</v>
+        <v>0.3607</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.2626</v>
+        <v>0.2067</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3713</v>
+        <v>0.154</v>
       </c>
       <c r="P4" t="n">
-        <v>1.6237</v>
+        <v>0.6959</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6237</v>
+        <v>0.6959</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2399</v>
+        <v>1.1341</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.275</v>
+        <v>0.2989</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0351</v>
+        <v>0.8351</v>
       </c>
       <c r="V4" t="n">
-        <v>1.0722</v>
+        <v>-1.3558</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.3558</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7607</v>
+        <v>1.9356</v>
       </c>
       <c r="E5" t="n">
-        <v>1.6242</v>
+        <v>1.4629</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1366</v>
+        <v>0.4726</v>
       </c>
       <c r="G5" t="n">
         <v>2.5951</v>
@@ -844,13 +844,13 @@
         <v>1.3917</v>
       </c>
       <c r="S5" t="n">
-        <v>0.181</v>
+        <v>0.3558</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.094</v>
+        <v>-0.2552</v>
       </c>
       <c r="U5" t="n">
-        <v>0.275</v>
+        <v>0.6111</v>
       </c>
       <c r="V5" t="n">
         <v>1.0722</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6421</v>
+        <v>0.7682</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.3255</v>
+        <v>-0.897</v>
       </c>
       <c r="F6" t="n">
-        <v>1.9676</v>
+        <v>1.6651</v>
       </c>
       <c r="G6" t="n">
         <v>-2.7196</v>
@@ -922,13 +922,13 @@
         <v>0.6959</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5215</v>
+        <v>0.6475</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7468</v>
+        <v>-0.3183</v>
       </c>
       <c r="U6" t="n">
-        <v>1.2683</v>
+        <v>0.9658</v>
       </c>
       <c r="V6" t="n">
         <v>2.1444</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0544</v>
+        <v>0.6083</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7331</v>
+        <v>-0.112</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7875</v>
+        <v>0.7203000000000001</v>
       </c>
       <c r="G7" t="n">
         <v>0.435</v>
@@ -1000,13 +1000,13 @@
         <v>1.3917</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0764</v>
+        <v>0.4775</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5737</v>
+        <v>0.0474</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4973</v>
+        <v>0.4301</v>
       </c>
       <c r="V7" t="n">
         <v>-0.5361</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.07439999999999999</v>
+        <v>0.2533</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6173999999999999</v>
+        <v>-0.1888</v>
       </c>
       <c r="F8" t="n">
-        <v>0.543</v>
+        <v>0.4422</v>
       </c>
       <c r="G8" t="n">
         <v>0.0064</v>
@@ -1078,13 +1078,13 @@
         <v>1.6237</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1735</v>
+        <v>0.1542</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8136</v>
+        <v>-0.3851</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6401</v>
+        <v>0.5392</v>
       </c>
       <c r="V8" t="n">
         <v>0.7886</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. THEIS</t>
+          <t>M. JAMES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8969</v>
+        <v>-0.4943</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8968</v>
+        <v>1.143</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0001</v>
+        <v>-1.6373</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.9674</v>
+        <v>2.4498</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.7094</v>
+        <v>2.6974</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.258</v>
+        <v>-0.2476</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.8082</v>
+        <v>4.0658</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.1323</v>
+        <v>3.835</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6758999999999999</v>
+        <v>0.2308</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.1592</v>
+        <v>-1.616</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.5771</v>
+        <v>-1.1377</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5821</v>
+        <v>-0.4783</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4639</v>
+        <v>-1.8556</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1598</v>
+        <v>-3.4793</v>
       </c>
       <c r="R9" t="n">
         <v>1.6237</v>
       </c>
       <c r="S9" t="n">
-        <v>1.5345</v>
+        <v>-0.2998</v>
       </c>
       <c r="T9" t="n">
-        <v>0.999</v>
+        <v>-0.2631</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5355</v>
+        <v>-0.0367</v>
       </c>
       <c r="V9" t="n">
-        <v>1.0722</v>
+        <v>-0.7886</v>
       </c>
       <c r="W9" t="n">
-        <v>1.0722</v>
+        <v>0.8197</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. JAMES</t>
+          <t>D. THEIS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1745</v>
+        <v>-2.1355</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8325</v>
+        <v>-1.7657</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.007</v>
+        <v>-0.3697</v>
       </c>
       <c r="G10" t="n">
-        <v>2.4498</v>
+        <v>-3.9674</v>
       </c>
       <c r="H10" t="n">
-        <v>2.6974</v>
+        <v>-2.7094</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2476</v>
+        <v>-1.258</v>
       </c>
       <c r="J10" t="n">
-        <v>4.0658</v>
+        <v>-1.8082</v>
       </c>
       <c r="K10" t="n">
-        <v>3.835</v>
+        <v>-1.1323</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2308</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.616</v>
+        <v>-2.1592</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.1377</v>
+        <v>-1.5771</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4783</v>
+        <v>-0.5821</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.8556</v>
+        <v>0.4639</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.4793</v>
+        <v>-1.1598</v>
       </c>
       <c r="R10" t="n">
         <v>1.6237</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9801</v>
+        <v>0.2959</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5737</v>
+        <v>0.13</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4063</v>
+        <v>0.1658</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.7886</v>
+        <v>1.0722</v>
       </c>
       <c r="W10" t="n">
-        <v>0.8197</v>
+        <v>1.0722</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,22 +1267,22 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>9.839199999999998</v>
+        <v>10.586</v>
       </c>
       <c r="E11" t="n">
-        <v>6.0648</v>
+        <v>6.8114</v>
       </c>
       <c r="F11" t="n">
         <v>3.7746</v>
       </c>
       <c r="G11" t="n">
-        <v>3.985800000000002</v>
+        <v>3.985800000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>4.7719</v>
+        <v>4.771899999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7865</v>
+        <v>-0.7864999999999998</v>
       </c>
       <c r="J11" t="n">
         <v>12.9779</v>
@@ -1291,13 +1291,13 @@
         <v>11.624</v>
       </c>
       <c r="L11" t="n">
-        <v>1.354099999999999</v>
+        <v>1.3541</v>
       </c>
       <c r="M11" t="n">
         <v>-8.9925</v>
       </c>
       <c r="N11" t="n">
-        <v>-6.852099999999999</v>
+        <v>-6.8521</v>
       </c>
       <c r="O11" t="n">
         <v>-2.1404</v>
@@ -1312,16 +1312,16 @@
         <v>11.5978</v>
       </c>
       <c r="S11" t="n">
-        <v>2.6139</v>
+        <v>3.3606</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.5507</v>
+        <v>-0.804</v>
       </c>
       <c r="U11" t="n">
-        <v>4.164700000000001</v>
+        <v>4.1645</v>
       </c>
       <c r="V11" t="n">
-        <v>4.399500000000001</v>
+        <v>4.3995</v>
       </c>
       <c r="W11" t="n">
         <v>7.3947</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.4886</v>
+        <v>5.3535</v>
       </c>
       <c r="E12" t="n">
-        <v>4.2075</v>
+        <v>3.9716</v>
       </c>
       <c r="F12" t="n">
-        <v>1.2811</v>
+        <v>1.3819</v>
       </c>
       <c r="G12" t="n">
         <v>4.9337</v>
@@ -1390,13 +1390,13 @@
         <v>1.8556</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.141</v>
+        <v>-0.2761</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2592</v>
+        <v>-0.4951</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1182</v>
+        <v>0.219</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.2554</v>
+        <v>0.0921</v>
       </c>
       <c r="E13" t="n">
-        <v>2.1734</v>
+        <v>1.9375</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.4289</v>
+        <v>-1.8455</v>
       </c>
       <c r="G13" t="n">
         <v>1.6781</v>
@@ -1468,13 +1468,13 @@
         <v>0.9278</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.485</v>
+        <v>-0.1375</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4086</v>
+        <v>-0.6445</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0764</v>
+        <v>0.507</v>
       </c>
       <c r="V13" t="n">
         <v>-2.1444</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. GRIGONIS</t>
+          <t>K. NUNN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.1409</v>
+        <v>0.077</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.1326</v>
+        <v>1.5604</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.0083</v>
+        <v>-1.4834</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.1512</v>
+        <v>2.6886</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.1512</v>
+        <v>2.1834</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>0.5052</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0168</v>
+        <v>5.5772</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0168</v>
+        <v>4.3293</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.2479</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.168</v>
+        <v>-2.8886</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.168</v>
+        <v>-2.146</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>-0.7426</v>
       </c>
       <c r="P14" t="n">
-        <v>0.232</v>
+        <v>-3.2473</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-4.871</v>
       </c>
       <c r="R14" t="n">
-        <v>0.232</v>
+        <v>1.6237</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1494</v>
+        <v>-0.0422</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1494</v>
+        <v>-0.896</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>0.8538</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.0722</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.7501</v>
       </c>
       <c r="X14" t="n">
         <v>-1.0722</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.1647</v>
+        <v>-0.2883</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.1972</v>
+        <v>0.2746</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.9675</v>
+        <v>-0.5629</v>
       </c>
       <c r="G15" t="n">
         <v>-0.9651</v>
@@ -1624,13 +1624,13 @@
         <v>1.6237</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.0552</v>
+        <v>-0.1788</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.2617</v>
+        <v>-0.7899</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2065</v>
+        <v>0.6111</v>
       </c>
       <c r="V15" t="n">
         <v>-0.5361</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>K. NUNN</t>
+          <t>M. GRIGONIS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.287</v>
+        <v>-1.0229</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9706</v>
+        <v>-0.0146</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.2576</v>
+        <v>-1.0083</v>
       </c>
       <c r="G16" t="n">
-        <v>2.6886</v>
+        <v>-0.1512</v>
       </c>
       <c r="H16" t="n">
-        <v>2.1834</v>
+        <v>-0.1512</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5052</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>5.5772</v>
+        <v>0.0168</v>
       </c>
       <c r="K16" t="n">
-        <v>4.3293</v>
+        <v>0.0168</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2479</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.8886</v>
+        <v>-0.168</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.146</v>
+        <v>-0.168</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.7426</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>-3.2473</v>
+        <v>0.232</v>
       </c>
       <c r="Q16" t="n">
-        <v>-4.871</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.6237</v>
+        <v>0.232</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.4062</v>
+        <v>-0.0314</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.4857</v>
+        <v>-0.0314</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0795</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>0.6778999999999999</v>
+        <v>-1.0722</v>
       </c>
       <c r="W16" t="n">
-        <v>1.7501</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
         <v>-1.0722</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.9196</v>
+        <v>-1.9683</v>
       </c>
       <c r="E17" t="n">
-        <v>-3.4996</v>
+        <v>-3.3816</v>
       </c>
       <c r="F17" t="n">
-        <v>1.58</v>
+        <v>1.4133</v>
       </c>
       <c r="G17" t="n">
         <v>-2.9128</v>
@@ -1780,13 +1780,13 @@
         <v>1.8556</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5294</v>
+        <v>0.4806</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.55</v>
+        <v>-0.4321</v>
       </c>
       <c r="U17" t="n">
-        <v>1.0794</v>
+        <v>0.9127</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>K. MITOGLOU</t>
+          <t>J. HERNANGOMEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.4316</v>
+        <v>-2.1057</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.6375</v>
+        <v>-1.1107</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7942</v>
+        <v>-0.995</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.4944</v>
+        <v>-4.1506</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.8812</v>
+        <v>-2.6181</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.6133</v>
+        <v>-1.5325</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.7244</v>
+        <v>-1.7877</v>
       </c>
       <c r="K18" t="n">
-        <v>1.2001</v>
+        <v>-0.9978</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.9246</v>
+        <v>-0.7899</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.77</v>
+        <v>-2.3629</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.0813</v>
+        <v>-1.6203</v>
       </c>
       <c r="O18" t="n">
-        <v>0.3113</v>
+        <v>-0.7426</v>
       </c>
       <c r="P18" t="n">
-        <v>0.6959</v>
+        <v>1.6237</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1598</v>
+        <v>-0.232</v>
       </c>
       <c r="R18" t="n">
         <v>1.8556</v>
       </c>
       <c r="S18" t="n">
-        <v>1.4391</v>
+        <v>-0.1149</v>
       </c>
       <c r="T18" t="n">
-        <v>1.2467</v>
+        <v>-0.6994</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1924</v>
+        <v>0.5845</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.0722</v>
+        <v>0.5361</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.6083</v>
       </c>
       <c r="X18" t="n">
         <v>-1.0722</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. HERNANGOMEZ</t>
+          <t>K. MITOGLOU</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.5439</v>
+        <v>-3.3359</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.1107</v>
+        <v>-2.699</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.4332</v>
+        <v>-0.6369</v>
       </c>
       <c r="G19" t="n">
-        <v>-4.1506</v>
+        <v>-3.4944</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.6181</v>
+        <v>-0.8812</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.5325</v>
+        <v>-2.6133</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.7877</v>
+        <v>-1.7244</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.9978</v>
+        <v>1.2001</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.7899</v>
+        <v>-2.9246</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.3629</v>
+        <v>-1.77</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.6203</v>
+        <v>-2.0813</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.7426</v>
+        <v>0.3113</v>
       </c>
       <c r="P19" t="n">
-        <v>1.6237</v>
+        <v>0.6959</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.232</v>
+        <v>-1.1598</v>
       </c>
       <c r="R19" t="n">
         <v>1.8556</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5531</v>
+        <v>0.5348000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6994</v>
+        <v>0.1852</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1463</v>
+        <v>0.3497</v>
       </c>
       <c r="V19" t="n">
-        <v>0.5361</v>
+        <v>-1.0722</v>
       </c>
       <c r="W19" t="n">
-        <v>1.6083</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>-1.0722</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.5846</v>
+        <v>-4.2815</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.5486</v>
+        <v>-4.3127</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0361</v>
+        <v>0.0311</v>
       </c>
       <c r="G20" t="n">
         <v>-1.6118</v>
@@ -2014,13 +2014,13 @@
         <v>0.9278</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7925</v>
+        <v>-0.4894</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5975</v>
+        <v>-0.3615</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.195</v>
+        <v>-0.1278</v>
       </c>
       <c r="V20" t="n">
         <v>-0.7886</v>
@@ -2047,22 +2047,22 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-9.8391</v>
+        <v>-7.48</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.7747</v>
+        <v>-3.7745</v>
       </c>
       <c r="F21" t="n">
-        <v>-6.064700000000001</v>
+        <v>-3.7057</v>
       </c>
       <c r="G21" t="n">
         <v>-3.985499999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>-4.772</v>
+        <v>-4.771999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>0.7863</v>
+        <v>0.7862999999999991</v>
       </c>
       <c r="J21" t="n">
         <v>8.9925</v>
@@ -2092,13 +2092,13 @@
         <v>12.7574</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.6139</v>
+        <v>-0.2549</v>
       </c>
       <c r="T21" t="n">
-        <v>-4.164800000000001</v>
+        <v>-4.1647</v>
       </c>
       <c r="U21" t="n">
-        <v>1.5509</v>
+        <v>3.91</v>
       </c>
       <c r="V21" t="n">
         <v>-4.3995</v>
